--- a/artfynd/A 26612-2025 artfynd.xlsx
+++ b/artfynd/A 26612-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>72035804</v>
       </c>
       <c r="B2" t="n">
-        <v>42566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -736,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498189.5197518347</v>
+        <v>498190</v>
       </c>
       <c r="R2" t="n">
-        <v>6997375.274292531</v>
+        <v>6997375</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -769,19 +764,9 @@
           <t>2018-06-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,16 +797,11 @@
         <v>72035813</v>
       </c>
       <c r="B3" t="n">
-        <v>42541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -870,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498189.5197518347</v>
+        <v>498190</v>
       </c>
       <c r="R3" t="n">
-        <v>6997375.274292531</v>
+        <v>6997375</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -903,19 +883,9 @@
           <t>2018-06-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,6 +910,351 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72035892</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vägkant SV Tjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>498190</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6997375</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Svensson, Anna Fohrman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72035833</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vägkant SV Tjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498190</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6997375</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Svensson, Anna Fohrman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>72035888</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vägkant SV Tjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498190</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6997375</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Svensson, Anna Fohrman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
